--- a/content/post/drafts/weekly-recap/2025Ruka/ladies_weekend.xlsx
+++ b/content/post/drafts/weekly-recap/2025Ruka/ladies_weekend.xlsx
@@ -737,13 +737,13 @@
         <v>61.2581128843742</v>
       </c>
       <c r="F2" t="n">
-        <v>184.5120605298</v>
+        <v>212.949877352734</v>
       </c>
       <c r="G2" t="n">
         <v>234</v>
       </c>
       <c r="H2" t="n">
-        <v>49.4879394702</v>
+        <v>21.050122647266</v>
       </c>
     </row>
     <row r="3">
@@ -763,13 +763,13 @@
         <v>95.3085857682113</v>
       </c>
       <c r="F3" t="n">
-        <v>127.983670945548</v>
+        <v>150.061679799274</v>
       </c>
       <c r="G3" t="n">
         <v>198</v>
       </c>
       <c r="H3" t="n">
-        <v>70.016329054452</v>
+        <v>47.938320200726</v>
       </c>
     </row>
     <row r="4">
@@ -789,13 +789,13 @@
         <v>15.6114448183848</v>
       </c>
       <c r="F4" t="n">
-        <v>197.850870088196</v>
+        <v>226.349286703655</v>
       </c>
       <c r="G4" t="n">
         <v>196</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.85087008819599</v>
+        <v>-30.349286703655</v>
       </c>
     </row>
     <row r="5">
@@ -815,13 +815,13 @@
         <v>76.1605024278517</v>
       </c>
       <c r="F5" t="n">
-        <v>128.91929196104</v>
+        <v>151.359804252345</v>
       </c>
       <c r="G5" t="n">
         <v>194</v>
       </c>
       <c r="H5" t="n">
-        <v>65.08070803896</v>
+        <v>42.640195747655</v>
       </c>
     </row>
     <row r="6">
@@ -841,13 +841,13 @@
         <v>48.6820481089837</v>
       </c>
       <c r="F6" t="n">
-        <v>176.858946138455</v>
+        <v>200</v>
       </c>
       <c r="G6" t="n">
         <v>180</v>
       </c>
       <c r="H6" t="n">
-        <v>3.141053861545</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="7">
@@ -867,13 +867,13 @@
         <v>104.971627440525</v>
       </c>
       <c r="F7" t="n">
-        <v>130.204171802345</v>
+        <v>152.947488504831</v>
       </c>
       <c r="G7" t="n">
         <v>170</v>
       </c>
       <c r="H7" t="n">
-        <v>39.795828197655</v>
+        <v>17.052511495169</v>
       </c>
     </row>
     <row r="8">
@@ -893,13 +893,13 @@
         <v>11.1901735968065</v>
       </c>
       <c r="F8" t="n">
-        <v>152.594443085999</v>
+        <v>177.571444243013</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
       </c>
       <c r="H8" t="n">
-        <v>5.40555691400101</v>
+        <v>-19.571444243013</v>
       </c>
     </row>
     <row r="9">
@@ -919,13 +919,13 @@
         <v>21.2600928935981</v>
       </c>
       <c r="F9" t="n">
-        <v>134.234078610259</v>
+        <v>157.983559374078</v>
       </c>
       <c r="G9" t="n">
         <v>146</v>
       </c>
       <c r="H9" t="n">
-        <v>11.765921389741</v>
+        <v>-11.983559374078</v>
       </c>
     </row>
     <row r="10">
@@ -945,13 +945,13 @@
         <v>58.5165324283278</v>
       </c>
       <c r="F10" t="n">
-        <v>140.948914097815</v>
+        <v>165.669671071456</v>
       </c>
       <c r="G10" t="n">
         <v>141</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0510859021850081</v>
+        <v>-24.669671071456</v>
       </c>
     </row>
     <row r="11">
@@ -971,13 +971,13 @@
         <v>-63.4340624184345</v>
       </c>
       <c r="F11" t="n">
-        <v>127.212075574235</v>
+        <v>148.454349177696</v>
       </c>
       <c r="G11" t="n">
         <v>141</v>
       </c>
       <c r="H11" t="n">
-        <v>13.787924425765</v>
+        <v>-7.454349177696</v>
       </c>
     </row>
     <row r="12">
@@ -997,13 +997,13 @@
         <v>118.652804113552</v>
       </c>
       <c r="F12" t="n">
-        <v>125.56194557913</v>
+        <v>147.547214639688</v>
       </c>
       <c r="G12" t="n">
         <v>141</v>
       </c>
       <c r="H12" t="n">
-        <v>15.43805442087</v>
+        <v>-6.54721463968801</v>
       </c>
     </row>
     <row r="13">
@@ -1023,13 +1023,13 @@
         <v>106.680132499334</v>
       </c>
       <c r="F13" t="n">
-        <v>82.6383190229012</v>
+        <v>96.0232085644709</v>
       </c>
       <c r="G13" t="n">
         <v>134</v>
       </c>
       <c r="H13" t="n">
-        <v>51.3616809770988</v>
+        <v>37.9767914355291</v>
       </c>
     </row>
     <row r="14">
@@ -1049,13 +1049,13 @@
         <v>59.0451758990762</v>
       </c>
       <c r="F14" t="n">
-        <v>91.4490245640843</v>
+        <v>103.88417819135</v>
       </c>
       <c r="G14" t="n">
         <v>134</v>
       </c>
       <c r="H14" t="n">
-        <v>42.5509754359157</v>
+        <v>30.11582180865</v>
       </c>
     </row>
     <row r="15">
@@ -1075,13 +1075,13 @@
         <v>126.81964404128</v>
       </c>
       <c r="F15" t="n">
-        <v>68.6842177843071</v>
+        <v>79.9660718147792</v>
       </c>
       <c r="G15" t="n">
         <v>132</v>
       </c>
       <c r="H15" t="n">
-        <v>63.3157822156929</v>
+        <v>52.0339281852208</v>
       </c>
     </row>
     <row r="16">
@@ -1101,13 +1101,13 @@
         <v>33.1784871230188</v>
       </c>
       <c r="F16" t="n">
-        <v>114.227956719251</v>
+        <v>134.198511034513</v>
       </c>
       <c r="G16" t="n">
         <v>124</v>
       </c>
       <c r="H16" t="n">
-        <v>9.772043280749</v>
+        <v>-10.198511034513</v>
       </c>
     </row>
     <row r="17">
@@ -1127,13 +1127,13 @@
         <v>49.6993334398073</v>
       </c>
       <c r="F17" t="n">
-        <v>101.303135332004</v>
+        <v>117.851114269085</v>
       </c>
       <c r="G17" t="n">
         <v>124</v>
       </c>
       <c r="H17" t="n">
-        <v>22.696864667996</v>
+        <v>6.148885730915</v>
       </c>
     </row>
     <row r="18">
@@ -1153,13 +1153,13 @@
         <v>53.1567312948921</v>
       </c>
       <c r="F18" t="n">
-        <v>72.9671064833315</v>
+        <v>84.5404963285726</v>
       </c>
       <c r="G18" t="n">
         <v>112</v>
       </c>
       <c r="H18" t="n">
-        <v>39.0328935166685</v>
+        <v>27.4595036714274</v>
       </c>
     </row>
     <row r="19">
@@ -1179,13 +1179,13 @@
         <v>78.2417518871191</v>
       </c>
       <c r="F19" t="n">
-        <v>89.2220286083683</v>
+        <v>103.546332234335</v>
       </c>
       <c r="G19" t="n">
         <v>107</v>
       </c>
       <c r="H19" t="n">
-        <v>17.7779713916317</v>
+        <v>3.453667765665</v>
       </c>
     </row>
     <row r="20">
@@ -1205,13 +1205,13 @@
         <v>-101.941761074267</v>
       </c>
       <c r="F20" t="n">
-        <v>176.433185878821</v>
+        <v>206.206683411078</v>
       </c>
       <c r="G20" t="n">
         <v>104</v>
       </c>
       <c r="H20" t="n">
-        <v>-72.433185878821</v>
+        <v>-102.206683411078</v>
       </c>
     </row>
     <row r="21">
@@ -1231,13 +1231,13 @@
         <v>98.1244291183166</v>
       </c>
       <c r="F21" t="n">
-        <v>65.1748586834949</v>
+        <v>73.9460778144997</v>
       </c>
       <c r="G21" t="n">
         <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>34.8251413165051</v>
+        <v>26.0539221855003</v>
       </c>
     </row>
     <row r="22">
@@ -1257,13 +1257,13 @@
         <v>48.9021364807952</v>
       </c>
       <c r="F22" t="n">
-        <v>135.855584268851</v>
+        <v>158.6017764641</v>
       </c>
       <c r="G22" t="n">
         <v>98</v>
       </c>
       <c r="H22" t="n">
-        <v>-37.855584268851</v>
+        <v>-60.6017764641</v>
       </c>
     </row>
     <row r="23">
@@ -1283,13 +1283,13 @@
         <v>101.783629359241</v>
       </c>
       <c r="F23" t="n">
-        <v>52.6876591142524</v>
+        <v>62.4020537708649</v>
       </c>
       <c r="G23" t="n">
         <v>98</v>
       </c>
       <c r="H23" t="n">
-        <v>45.3123408857476</v>
+        <v>35.5979462291351</v>
       </c>
     </row>
     <row r="24">
@@ -1309,13 +1309,13 @@
         <v>146.879089442982</v>
       </c>
       <c r="F24" t="n">
-        <v>31.3035486545315</v>
+        <v>35.8292780219999</v>
       </c>
       <c r="G24" t="n">
         <v>96</v>
       </c>
       <c r="H24" t="n">
-        <v>64.6964513454685</v>
+        <v>60.1707219780001</v>
       </c>
     </row>
     <row r="25">
@@ -1335,13 +1335,13 @@
         <v>111.261474725588</v>
       </c>
       <c r="F25" t="n">
-        <v>58.1902735873559</v>
+        <v>65.9977949909207</v>
       </c>
       <c r="G25" t="n">
         <v>95</v>
       </c>
       <c r="H25" t="n">
-        <v>36.8097264126441</v>
+        <v>29.0022050090793</v>
       </c>
     </row>
     <row r="26">
@@ -1361,13 +1361,13 @@
         <v>8.75019405777152</v>
       </c>
       <c r="F26" t="n">
-        <v>147.785697711092</v>
+        <v>172.638799655417</v>
       </c>
       <c r="G26" t="n">
         <v>94</v>
       </c>
       <c r="H26" t="n">
-        <v>-53.785697711092</v>
+        <v>-78.638799655417</v>
       </c>
     </row>
     <row r="27">
@@ -1387,13 +1387,13 @@
         <v>-8.45104641544958</v>
       </c>
       <c r="F27" t="n">
-        <v>75.489033617764</v>
+        <v>87.9692710743438</v>
       </c>
       <c r="G27" t="n">
         <v>93</v>
       </c>
       <c r="H27" t="n">
-        <v>17.510966382236</v>
+        <v>5.03072892565621</v>
       </c>
     </row>
     <row r="28">
@@ -1413,13 +1413,13 @@
         <v>56.402302277661</v>
       </c>
       <c r="F28" t="n">
-        <v>38.8970566813046</v>
+        <v>45.3322813683187</v>
       </c>
       <c r="G28" t="n">
         <v>92</v>
       </c>
       <c r="H28" t="n">
-        <v>53.1029433186954</v>
+        <v>46.6677186316813</v>
       </c>
     </row>
     <row r="29">
@@ -1439,13 +1439,13 @@
         <v>-17.2188736184489</v>
       </c>
       <c r="F29" t="n">
-        <v>93.5257957393434</v>
+        <v>106.240714764375</v>
       </c>
       <c r="G29" t="n">
         <v>88</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.52579573934339</v>
+        <v>-18.240714764375</v>
       </c>
     </row>
     <row r="30">
@@ -1465,13 +1465,13 @@
         <v>73.63857713381</v>
       </c>
       <c r="F30" t="n">
-        <v>83.6231117065889</v>
+        <v>97.3134486879327</v>
       </c>
       <c r="G30" t="n">
         <v>83</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.623111706588901</v>
+        <v>-14.3134486879327</v>
       </c>
     </row>
     <row r="31">
@@ -1491,13 +1491,13 @@
         <v>-49.5522292122137</v>
       </c>
       <c r="F31" t="n">
-        <v>86.0733215696159</v>
+        <v>100.895152365981</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.0733215696159</v>
+        <v>-22.895152365981</v>
       </c>
     </row>
     <row r="32">
@@ -1517,13 +1517,13 @@
         <v>18.3889149014306</v>
       </c>
       <c r="F32" t="n">
-        <v>36.5325357104294</v>
+        <v>42.625044133681</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
       </c>
       <c r="H32" t="n">
-        <v>38.4674642895706</v>
+        <v>32.374955866319</v>
       </c>
     </row>
     <row r="33">
@@ -1543,13 +1543,13 @@
         <v>85.2335632918764</v>
       </c>
       <c r="F33" t="n">
-        <v>56.9033010684198</v>
+        <v>66.5292369904658</v>
       </c>
       <c r="G33" t="n">
         <v>74</v>
       </c>
       <c r="H33" t="n">
-        <v>17.0966989315802</v>
+        <v>7.4707630095342</v>
       </c>
     </row>
     <row r="34">
@@ -1569,13 +1569,13 @@
         <v>61.9408790179257</v>
       </c>
       <c r="F34" t="n">
-        <v>63.9885849350811</v>
+        <v>73.6870468277128</v>
       </c>
       <c r="G34" t="n">
         <v>74</v>
       </c>
       <c r="H34" t="n">
-        <v>10.0114150649189</v>
+        <v>0.312953172287195</v>
       </c>
     </row>
     <row r="35">
@@ -1595,13 +1595,13 @@
         <v>42.119150275304</v>
       </c>
       <c r="F35" t="n">
-        <v>68.961192035993</v>
+        <v>80.852286036932</v>
       </c>
       <c r="G35" t="n">
         <v>73</v>
       </c>
       <c r="H35" t="n">
-        <v>4.03880796400701</v>
+        <v>-7.852286036932</v>
       </c>
     </row>
     <row r="36">
@@ -1621,13 +1621,13 @@
         <v>129.185803473517</v>
       </c>
       <c r="F36" t="n">
-        <v>17.6321147622695</v>
+        <v>20.0945507256666</v>
       </c>
       <c r="G36" t="n">
         <v>69</v>
       </c>
       <c r="H36" t="n">
-        <v>51.3678852377305</v>
+        <v>48.9054492743334</v>
       </c>
     </row>
     <row r="37">
@@ -1647,13 +1647,13 @@
         <v>126.850897030302</v>
       </c>
       <c r="F37" t="n">
-        <v>22.730823982568</v>
+        <v>25.7806703541982</v>
       </c>
       <c r="G37" t="n">
         <v>66</v>
       </c>
       <c r="H37" t="n">
-        <v>43.269176017432</v>
+        <v>40.2193296458018</v>
       </c>
     </row>
     <row r="38">
@@ -1673,13 +1673,13 @@
         <v>52.6899659640483</v>
       </c>
       <c r="F38" t="n">
-        <v>33.9366918943854</v>
+        <v>40.5916409471636</v>
       </c>
       <c r="G38" t="n">
         <v>66</v>
       </c>
       <c r="H38" t="n">
-        <v>32.0633081056146</v>
+        <v>25.4083590528364</v>
       </c>
     </row>
     <row r="39">
@@ -1699,13 +1699,13 @@
         <v>19.0787610267812</v>
       </c>
       <c r="F39" t="n">
-        <v>45.966268247928</v>
+        <v>52.2701787347648</v>
       </c>
       <c r="G39" t="n">
         <v>63</v>
       </c>
       <c r="H39" t="n">
-        <v>17.033731752072</v>
+        <v>10.7298212652352</v>
       </c>
     </row>
     <row r="40">
@@ -1725,13 +1725,13 @@
         <v>79.1403135177009</v>
       </c>
       <c r="F40" t="n">
-        <v>12.379210295953</v>
+        <v>14.6120929615921</v>
       </c>
       <c r="G40" t="n">
         <v>62</v>
       </c>
       <c r="H40" t="n">
-        <v>49.620789704047</v>
+        <v>47.3879070384079</v>
       </c>
     </row>
     <row r="41">
@@ -1751,13 +1751,13 @@
         <v>-38.167397136654</v>
       </c>
       <c r="F41" t="n">
-        <v>83.9478849531095</v>
+        <v>98.7183017457819</v>
       </c>
       <c r="G41" t="n">
         <v>58</v>
       </c>
       <c r="H41" t="n">
-        <v>-25.9478849531095</v>
+        <v>-40.7183017457819</v>
       </c>
     </row>
     <row r="42">
@@ -1777,13 +1777,13 @@
         <v>82.5360628451044</v>
       </c>
       <c r="F42" t="n">
-        <v>38.3166776824174</v>
+        <v>43.4997446004487</v>
       </c>
       <c r="G42" t="n">
         <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15.6833223175826</v>
+        <v>10.5002553995513</v>
       </c>
     </row>
     <row r="43">
@@ -1803,13 +1803,13 @@
         <v>-35.3554718722773</v>
       </c>
       <c r="F43" t="n">
-        <v>86.7239921997171</v>
+        <v>101.153912564123</v>
       </c>
       <c r="G43" t="n">
         <v>52</v>
       </c>
       <c r="H43" t="n">
-        <v>-34.7239921997171</v>
+        <v>-49.153912564123</v>
       </c>
     </row>
     <row r="44">
@@ -1829,13 +1829,13 @@
         <v>33.7597174858399</v>
       </c>
       <c r="F44" t="n">
-        <v>63.4456166989302</v>
+        <v>72.1605607270312</v>
       </c>
       <c r="G44" t="n">
         <v>50</v>
       </c>
       <c r="H44" t="n">
-        <v>-13.4456166989302</v>
+        <v>-22.1605607270312</v>
       </c>
     </row>
     <row r="45">
@@ -1855,13 +1855,13 @@
         <v>43.146685649122</v>
       </c>
       <c r="F45" t="n">
-        <v>39.9664756052368</v>
+        <v>45.3288685701796</v>
       </c>
       <c r="G45" t="n">
         <v>48</v>
       </c>
       <c r="H45" t="n">
-        <v>8.0335243947632</v>
+        <v>2.6711314298204</v>
       </c>
     </row>
     <row r="46">
@@ -1881,13 +1881,13 @@
         <v>70.9069672010341</v>
       </c>
       <c r="F46" t="n">
-        <v>4.49084560637728</v>
+        <v>5.38441389666852</v>
       </c>
       <c r="G46" t="n">
         <v>47</v>
       </c>
       <c r="H46" t="n">
-        <v>42.5091543936227</v>
+        <v>41.6155861033315</v>
       </c>
     </row>
     <row r="47">
@@ -1907,13 +1907,13 @@
         <v>-25.7867209399533</v>
       </c>
       <c r="F47" t="n">
-        <v>34.9262078666091</v>
+        <v>40.8579804694656</v>
       </c>
       <c r="G47" t="n">
         <v>45</v>
       </c>
       <c r="H47" t="n">
-        <v>10.0737921333909</v>
+        <v>4.1420195305344</v>
       </c>
     </row>
     <row r="48">
@@ -1933,13 +1933,13 @@
         <v>30.6941916615376</v>
       </c>
       <c r="F48" t="n">
-        <v>31.9731673667572</v>
+        <v>36.2630799787158</v>
       </c>
       <c r="G48" t="n">
         <v>40</v>
       </c>
       <c r="H48" t="n">
-        <v>8.0268326332428</v>
+        <v>3.7369200212842</v>
       </c>
     </row>
     <row r="49">
@@ -1959,13 +1959,13 @@
         <v>58.4555987556014</v>
       </c>
       <c r="F49" t="n">
-        <v>20.9661547106393</v>
+        <v>23.815794043384</v>
       </c>
       <c r="G49" t="n">
         <v>38</v>
       </c>
       <c r="H49" t="n">
-        <v>17.0338452893607</v>
+        <v>14.184205956616</v>
       </c>
     </row>
     <row r="50">
@@ -1985,13 +1985,13 @@
         <v>63.9091330966887</v>
       </c>
       <c r="F50" t="n">
-        <v>25.8756218281133</v>
+        <v>29.4326566688867</v>
       </c>
       <c r="G50" t="n">
         <v>38</v>
       </c>
       <c r="H50" t="n">
-        <v>12.1243781718867</v>
+        <v>8.5673433311133</v>
       </c>
     </row>
     <row r="51">
@@ -2011,13 +2011,13 @@
         <v>43.541683653141</v>
       </c>
       <c r="F51" t="n">
-        <v>46.113710703638</v>
+        <v>52.5947996223326</v>
       </c>
       <c r="G51" t="n">
         <v>36</v>
       </c>
       <c r="H51" t="n">
-        <v>-10.113710703638</v>
+        <v>-16.5947996223326</v>
       </c>
     </row>
     <row r="52">
@@ -2037,13 +2037,13 @@
         <v>-132.140370707791</v>
       </c>
       <c r="F52" t="n">
-        <v>70.3897205275162</v>
+        <v>80.7029982880435</v>
       </c>
       <c r="G52" t="n">
         <v>34</v>
       </c>
       <c r="H52" t="n">
-        <v>-36.3897205275162</v>
+        <v>-46.7029982880435</v>
       </c>
     </row>
     <row r="53">
@@ -2063,13 +2063,13 @@
         <v>-38.2790464578457</v>
       </c>
       <c r="F53" t="n">
-        <v>40.8264817907627</v>
+        <v>47.5714804755614</v>
       </c>
       <c r="G53" t="n">
         <v>33</v>
       </c>
       <c r="H53" t="n">
-        <v>-7.8264817907627</v>
+        <v>-14.5714804755614</v>
       </c>
     </row>
     <row r="54">
@@ -2089,13 +2089,13 @@
         <v>39.5277692709055</v>
       </c>
       <c r="F54" t="n">
-        <v>15.3337716890484</v>
+        <v>19.5818477113001</v>
       </c>
       <c r="G54" t="n">
         <v>31</v>
       </c>
       <c r="H54" t="n">
-        <v>15.6662283109516</v>
+        <v>11.4181522886999</v>
       </c>
     </row>
     <row r="55">
@@ -2115,13 +2115,13 @@
         <v>42.4331160326142</v>
       </c>
       <c r="F55" t="n">
-        <v>-9.32251583011153</v>
+        <v>1.60487108971242</v>
       </c>
       <c r="G55" t="n">
         <v>30</v>
       </c>
       <c r="H55" t="n">
-        <v>39.3225158301115</v>
+        <v>28.3951289102876</v>
       </c>
     </row>
     <row r="56">
@@ -2141,13 +2141,13 @@
         <v>-16.5551750493</v>
       </c>
       <c r="F56" t="n">
-        <v>27.6301846056842</v>
+        <v>31.7233728589896</v>
       </c>
       <c r="G56" t="n">
         <v>29</v>
       </c>
       <c r="H56" t="n">
-        <v>1.3698153943158</v>
+        <v>-2.7233728589896</v>
       </c>
     </row>
     <row r="57">
@@ -2189,13 +2189,13 @@
         <v>38.1681980454848</v>
       </c>
       <c r="F58" t="n">
-        <v>20.9114672651301</v>
+        <v>23.7172064065237</v>
       </c>
       <c r="G58" t="n">
         <v>26</v>
       </c>
       <c r="H58" t="n">
-        <v>5.0885327348699</v>
+        <v>2.2827935934763</v>
       </c>
     </row>
     <row r="59">
@@ -2215,13 +2215,13 @@
         <v>-2.8313256448148</v>
       </c>
       <c r="F59" t="n">
-        <v>13.8451472335982</v>
+        <v>16.2104995744989</v>
       </c>
       <c r="G59" t="n">
         <v>25</v>
       </c>
       <c r="H59" t="n">
-        <v>11.1548527664018</v>
+        <v>8.7895004255011</v>
       </c>
     </row>
     <row r="60">
@@ -2241,13 +2241,13 @@
         <v>-74.7789351645181</v>
       </c>
       <c r="F60" t="n">
-        <v>12.3779882630005</v>
+        <v>14.1804017157323</v>
       </c>
       <c r="G60" t="n">
         <v>24</v>
       </c>
       <c r="H60" t="n">
-        <v>11.6220117369995</v>
+        <v>9.8195982842677</v>
       </c>
     </row>
     <row r="61">
@@ -2267,13 +2267,13 @@
         <v>-82.40897011427</v>
       </c>
       <c r="F61" t="n">
-        <v>45.0048422629265</v>
+        <v>51.8513526172956</v>
       </c>
       <c r="G61" t="n">
         <v>20</v>
       </c>
       <c r="H61" t="n">
-        <v>-25.0048422629265</v>
+        <v>-31.8513526172956</v>
       </c>
     </row>
     <row r="62">
@@ -2293,13 +2293,13 @@
         <v>0.714112367946882</v>
       </c>
       <c r="F62" t="n">
-        <v>34.1113631750156</v>
+        <v>38.7724917576239</v>
       </c>
       <c r="G62" t="n">
         <v>19</v>
       </c>
       <c r="H62" t="n">
-        <v>-15.1113631750156</v>
+        <v>-19.7724917576239</v>
       </c>
     </row>
     <row r="63">
@@ -2319,13 +2319,13 @@
         <v>-2.07641528586851</v>
       </c>
       <c r="F63" t="n">
-        <v>9.7089845931137</v>
+        <v>14.1529865171698</v>
       </c>
       <c r="G63" t="n">
         <v>18</v>
       </c>
       <c r="H63" t="n">
-        <v>8.2910154068863</v>
+        <v>3.8470134828302</v>
       </c>
     </row>
     <row r="64">
@@ -2345,13 +2345,13 @@
         <v>-36.492836843767</v>
       </c>
       <c r="F64" t="n">
-        <v>9.24697111447145</v>
+        <v>10.7046178433273</v>
       </c>
       <c r="G64" t="n">
         <v>16</v>
       </c>
       <c r="H64" t="n">
-        <v>6.75302888552855</v>
+        <v>5.2953821566727</v>
       </c>
     </row>
     <row r="65">
@@ -2371,13 +2371,13 @@
         <v>-21.1423991768106</v>
       </c>
       <c r="F65" t="n">
-        <v>-2.47425065927014</v>
+        <v>0.382422476441757</v>
       </c>
       <c r="G65" t="n">
         <v>14</v>
       </c>
       <c r="H65" t="n">
-        <v>16.4742506592701</v>
+        <v>13.6175775235582</v>
       </c>
     </row>
     <row r="66">
@@ -2397,13 +2397,13 @@
         <v>-111.732052643131</v>
       </c>
       <c r="F66" t="n">
-        <v>56.6307088484121</v>
+        <v>65.4245265398423</v>
       </c>
       <c r="G66" t="n">
         <v>13</v>
       </c>
       <c r="H66" t="n">
-        <v>-43.6307088484121</v>
+        <v>-52.4245265398423</v>
       </c>
     </row>
     <row r="67">
@@ -2423,13 +2423,13 @@
         <v>7.38094180473445</v>
       </c>
       <c r="F67" t="n">
-        <v>27.2072238091715</v>
+        <v>31.0458483529137</v>
       </c>
       <c r="G67" t="n">
         <v>12</v>
       </c>
       <c r="H67" t="n">
-        <v>-15.2072238091715</v>
+        <v>-19.0458483529137</v>
       </c>
     </row>
     <row r="68">
@@ -2467,13 +2467,13 @@
         <v>-41.8018918821613</v>
       </c>
       <c r="F69" t="n">
-        <v>24.0132267741122</v>
+        <v>27.3668252507009</v>
       </c>
       <c r="G69" t="n">
         <v>11</v>
       </c>
       <c r="H69" t="n">
-        <v>-13.0132267741122</v>
+        <v>-16.3668252507009</v>
       </c>
     </row>
     <row r="70">
@@ -2493,13 +2493,13 @@
         <v>-54.6841752052128</v>
       </c>
       <c r="F70" t="n">
-        <v>7.01146120303135</v>
+        <v>8.01632426991532</v>
       </c>
       <c r="G70" t="n">
         <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>2.98853879696865</v>
+        <v>1.98367573008468</v>
       </c>
     </row>
     <row r="71">
@@ -2519,13 +2519,13 @@
         <v>-83.9174064849728</v>
       </c>
       <c r="F71" t="n">
-        <v>9.04701377342125</v>
+        <v>10.5794710033199</v>
       </c>
       <c r="G71" t="n">
         <v>9</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.0470137734212503</v>
+        <v>-1.5794710033199</v>
       </c>
     </row>
     <row r="72">
@@ -2589,13 +2589,13 @@
         <v>-28.6395782256809</v>
       </c>
       <c r="F74" t="n">
-        <v>8.26541967304588</v>
+        <v>9.41973762808958</v>
       </c>
       <c r="G74" t="n">
         <v>7</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.26541967304588</v>
+        <v>-2.41973762808958</v>
       </c>
     </row>
     <row r="75">
@@ -2615,13 +2615,13 @@
         <v>-89.3954293772529</v>
       </c>
       <c r="F75" t="n">
-        <v>3.64173696405635</v>
+        <v>5.6327876267012</v>
       </c>
       <c r="G75" t="n">
         <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>2.35826303594365</v>
+        <v>0.3672123732988</v>
       </c>
     </row>
     <row r="76">
@@ -2641,13 +2641,13 @@
         <v>-99.057997776207</v>
       </c>
       <c r="F76" t="n">
-        <v>25.0225868164665</v>
+        <v>28.8737708639829</v>
       </c>
       <c r="G76" t="n">
         <v>5</v>
       </c>
       <c r="H76" t="n">
-        <v>-20.0225868164665</v>
+        <v>-23.8737708639829</v>
       </c>
     </row>
     <row r="77">
@@ -2667,13 +2667,13 @@
         <v>-91.5172547380398</v>
       </c>
       <c r="F77" t="n">
-        <v>-28.3033842977837</v>
+        <v>1.00509897499774</v>
       </c>
       <c r="G77" t="n">
         <v>4</v>
       </c>
       <c r="H77" t="n">
-        <v>32.3033842977837</v>
+        <v>2.99490102500226</v>
       </c>
     </row>
     <row r="78">
@@ -2737,13 +2737,13 @@
         <v>-44.3410061985467</v>
       </c>
       <c r="F80" t="n">
-        <v>-19.6316301844901</v>
+        <v>3.2831161463983</v>
       </c>
       <c r="G80" t="n">
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>21.6316301844901</v>
+        <v>-1.2831161463983</v>
       </c>
     </row>
     <row r="81">
@@ -2785,13 +2785,13 @@
         <v>-50.2390734575606</v>
       </c>
       <c r="F82" t="n">
-        <v>32.3860638392939</v>
+        <v>37.551632337383</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>-31.3860638392939</v>
+        <v>-36.551632337383</v>
       </c>
     </row>
     <row r="83">
@@ -2811,13 +2811,13 @@
         <v>-83.2046705740504</v>
       </c>
       <c r="F83" t="n">
-        <v>-25.4628069749505</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>26.4628069749505</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2837,13 +2837,13 @@
         <v>-161.590677217721</v>
       </c>
       <c r="F84" t="n">
-        <v>0.969893716197443</v>
+        <v>5.72883752632151</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.969893716197443</v>
+        <v>-5.72883752632151</v>
       </c>
     </row>
     <row r="85">
@@ -2863,13 +2863,13 @@
         <v>-110.995389065813</v>
       </c>
       <c r="F85" t="n">
-        <v>-11.853822147981</v>
+        <v>3.0613225418933</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>11.853822147981</v>
+        <v>-3.0613225418933</v>
       </c>
     </row>
     <row r="86">
@@ -2889,13 +2889,13 @@
         <v>-47.8876372274494</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.175962770175843</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.175962770175843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2955,13 +2955,13 @@
         <v>-119.946816059037</v>
       </c>
       <c r="F89" t="n">
-        <v>-21.4830443828482</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>21.4830443828482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2981,13 +2981,13 @@
         <v>-78.199411277782</v>
       </c>
       <c r="F90" t="n">
-        <v>-16.6226840946488</v>
+        <v>1.75882352808337</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>16.6226840946488</v>
+        <v>-1.75882352808337</v>
       </c>
     </row>
     <row r="91">
@@ -3007,13 +3007,13 @@
         <v>-53.9579507035742</v>
       </c>
       <c r="F91" t="n">
-        <v>6.35972270600612</v>
+        <v>7.40204787310546</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-6.35972270600612</v>
+        <v>-7.40204787310546</v>
       </c>
     </row>
     <row r="92">
@@ -3033,13 +3033,13 @@
         <v>-68.0230171029696</v>
       </c>
       <c r="F92" t="n">
-        <v>-27.6099177665872</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>27.6099177665872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3055,13 +3055,13 @@
       </c>
       <c r="E93"/>
       <c r="F93" t="n">
-        <v>2.06794542701618</v>
+        <v>2.51089684563639</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-2.06794542701618</v>
+        <v>-2.51089684563639</v>
       </c>
     </row>
   </sheetData>
